--- a/docs/result/analysis/enrollment-burst-test-spin-lock-result.xlsx
+++ b/docs/result/analysis/enrollment-burst-test-spin-lock-result.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sangja/Projects/concurrency-control-benchmarks/docs/result/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511EFDB9-5E9E-7A44-AD71-9831BC192CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9583BEA-B5EA-FC45-B9F7-A90C8C8E23EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="28200" xr2:uid="{829354C8-DEED-BD4A-88FD-415D5A61907D}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14700" windowHeight="18460" activeTab="2" xr2:uid="{829354C8-DEED-BD4A-88FD-415D5A61907D}"/>
   </bookViews>
   <sheets>
     <sheet name="Spin Lock" sheetId="1" r:id="rId1"/>
     <sheet name="TPS" sheetId="2" r:id="rId2"/>
+    <sheet name="Mean Latency" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>TPS (request/sec)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,11 +68,75 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>평균 TPS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Vuser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>취합 TPS (request/sec)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mean TPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peek TPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Worst Mean TPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall Mean TPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best Mean TPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Average Peak TPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mean Latency (ms)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>취합 Mean Latency (ms)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mean Latency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Worst Mean Latency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall Mean Latency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best Mean Latency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95th Percentile (추정치)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Worst 95th Percentile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall 95th Percentile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best 95th Percentile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,140 +534,700 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE196A4-CB6E-9740-BA12-8F5D37C430EC}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4">
         <v>500</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="C4">
+        <v>41.5</v>
+      </c>
+      <c r="D4">
+        <v>115.5</v>
+      </c>
+      <c r="H4">
+        <v>500</v>
+      </c>
+      <c r="I4">
+        <f>MIN(C4,C7,C10,C13,C16)</f>
+        <v>41.5</v>
+      </c>
+      <c r="J4">
+        <f>AVERAGE(C4,C7,C10,C13,C16)</f>
+        <v>49</v>
+      </c>
+      <c r="K4">
+        <f>MAX(C4,C7,C10,C13,C16)</f>
+        <v>62.3</v>
+      </c>
+      <c r="L4">
+        <f>AVERAGE(D4,D7,D10,D13,D16)</f>
+        <v>126.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5">
         <v>800</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5">
+        <v>57</v>
+      </c>
+      <c r="D5">
+        <v>196.5</v>
+      </c>
+      <c r="H5">
+        <v>800</v>
+      </c>
+      <c r="I5">
+        <f>MIN(C5,C8,C11,C14,C17)</f>
+        <v>57</v>
+      </c>
+      <c r="J5">
+        <f>AVERAGE(C5,C8,C11,C14,C17)</f>
+        <v>87.1</v>
+      </c>
+      <c r="K5">
+        <f>MAX(C5,C8,C11,C14,C17)</f>
+        <v>99.7</v>
+      </c>
+      <c r="L5">
+        <f>AVERAGE(D5,D8,D11,D14,D17)</f>
+        <v>229.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="C6">
+        <v>99.7</v>
+      </c>
+      <c r="D6">
+        <v>159</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <f>MIN(C6,C9,C12,C15,C18)</f>
+        <v>83.1</v>
+      </c>
+      <c r="J6">
+        <f>AVERAGE(C6,C9,C12,C15,C18)</f>
+        <v>96.32</v>
+      </c>
+      <c r="K6">
+        <f>MAX(C6,C9,C12,C15,C18)</f>
+        <v>99.7</v>
+      </c>
+      <c r="L6">
+        <f>AVERAGE(D6,D9,D12,D15,D18)</f>
+        <v>213.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B7">
         <v>500</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C7">
+        <v>49.9</v>
+      </c>
+      <c r="D7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8">
         <v>800</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="C8">
+        <v>79.7</v>
+      </c>
+      <c r="D8">
+        <v>199.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9">
         <v>1000</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="C9">
+        <v>99.4</v>
+      </c>
+      <c r="D9">
+        <v>234.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B10">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="C10">
+        <v>62.3</v>
+      </c>
+      <c r="D10">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11">
         <v>800</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="C11">
+        <v>99.7</v>
+      </c>
+      <c r="D11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12">
         <v>1000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="C12">
+        <v>99.7</v>
+      </c>
+      <c r="D12">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B13">
         <v>500</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="C13">
+        <v>41.5</v>
+      </c>
+      <c r="D13">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1"/>
       <c r="B14">
         <v>800</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="C14">
+        <v>99.5</v>
+      </c>
+      <c r="D14">
+        <v>288.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1"/>
       <c r="B15">
         <v>1000</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="C15">
+        <v>83.1</v>
+      </c>
+      <c r="D15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B16">
         <v>500</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16">
+        <v>49.8</v>
+      </c>
+      <c r="D16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1"/>
       <c r="B17">
         <v>800</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17">
+        <v>99.6</v>
+      </c>
+      <c r="D17">
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1"/>
       <c r="B18">
         <v>1000</v>
       </c>
+      <c r="C18">
+        <v>99.7</v>
+      </c>
+      <c r="D18">
+        <v>221</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="H1:L2"/>
     <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A1:C2"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A1:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C67DF5B-71C1-464D-94D3-B28EAF171A95}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="C4">
+        <v>388.85</v>
+      </c>
+      <c r="D4">
+        <v>1021.33</v>
+      </c>
+      <c r="H4">
+        <v>500</v>
+      </c>
+      <c r="I4">
+        <f>MAX(C4,C7,C10,C13,C16)</f>
+        <v>712.17</v>
+      </c>
+      <c r="J4">
+        <f>AVERAGE(C4,C7,C10,C13,C16)</f>
+        <v>598.21199999999999</v>
+      </c>
+      <c r="K4">
+        <f>MIN(C4,C7,C10,C13,C16)</f>
+        <v>388.85</v>
+      </c>
+      <c r="L4">
+        <f>MAX(D4,D7,D10,D13,D16)</f>
+        <v>1577.8</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGE(D4,D7,D10,D13,D16)</f>
+        <v>1359.3319999999999</v>
+      </c>
+      <c r="N4">
+        <f>MIN(D4,D7,D10,D13,D16)</f>
+        <v>1021.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="1"/>
+      <c r="B5">
+        <v>800</v>
+      </c>
+      <c r="C5">
+        <v>846.03</v>
+      </c>
+      <c r="D5">
+        <v>1770.78</v>
+      </c>
+      <c r="H5">
+        <v>800</v>
+      </c>
+      <c r="I5">
+        <f>MAX(C5,C8,C11,C14,C17)</f>
+        <v>1197.05</v>
+      </c>
+      <c r="J5">
+        <f>AVERAGE(C5,C8,C11,C14,C17)</f>
+        <v>1049.306</v>
+      </c>
+      <c r="K5">
+        <f>MIN(C5,C8,C11,C14,C17)</f>
+        <v>846.03</v>
+      </c>
+      <c r="L5">
+        <f>MAX(D5,D8,D11,D14,D17)</f>
+        <v>2195.4</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE(D5,D8,D11,D14,D17)</f>
+        <v>1980.902</v>
+      </c>
+      <c r="N5">
+        <f>MIN(D5,D8,D11,D14,D17)</f>
+        <v>1759.74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="1"/>
+      <c r="B6">
+        <v>1000</v>
+      </c>
+      <c r="C6">
+        <v>1092.03</v>
+      </c>
+      <c r="D6">
+        <v>1935.02</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <f>MAX(C6,C9,C12,C15,C18)</f>
+        <v>1234.6099999999999</v>
+      </c>
+      <c r="J6">
+        <f>AVERAGE(C6,C9,C12,C15,C18)</f>
+        <v>1117.79</v>
+      </c>
+      <c r="K6">
+        <f>MIN(C6,C9,C12,C15,C18)</f>
+        <v>911.19</v>
+      </c>
+      <c r="L6">
+        <f>MAX(D6,D9,D12,D15,D18)</f>
+        <v>2390.83</v>
+      </c>
+      <c r="M6">
+        <f>AVERAGE(D6,D9,D12,D15,D18)</f>
+        <v>2147.4879999999998</v>
+      </c>
+      <c r="N6">
+        <f>MIN(D6,D9,D12,D15,D18)</f>
+        <v>1836.59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>500</v>
+      </c>
+      <c r="C7">
+        <v>712.17</v>
+      </c>
+      <c r="D7">
+        <v>1577.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="1"/>
+      <c r="B8">
+        <v>800</v>
+      </c>
+      <c r="C8">
+        <v>1005.91</v>
+      </c>
+      <c r="D8">
+        <v>1759.74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="1"/>
+      <c r="B9">
+        <v>1000</v>
+      </c>
+      <c r="C9">
+        <v>1129.4000000000001</v>
+      </c>
+      <c r="D9">
+        <v>2390.83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>500</v>
+      </c>
+      <c r="C10">
+        <v>609.98</v>
+      </c>
+      <c r="D10">
+        <v>1430.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="1"/>
+      <c r="B11">
+        <v>800</v>
+      </c>
+      <c r="C11">
+        <v>1163.3699999999999</v>
+      </c>
+      <c r="D11">
+        <v>2174.0300000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="1"/>
+      <c r="B12">
+        <v>1000</v>
+      </c>
+      <c r="C12">
+        <v>911.19</v>
+      </c>
+      <c r="D12">
+        <v>1836.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>500</v>
+      </c>
+      <c r="C13">
+        <v>624.52</v>
+      </c>
+      <c r="D13">
+        <v>1426.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1"/>
+      <c r="B14">
+        <v>800</v>
+      </c>
+      <c r="C14">
+        <v>1034.17</v>
+      </c>
+      <c r="D14">
+        <v>2004.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="1"/>
+      <c r="B15">
+        <v>1000</v>
+      </c>
+      <c r="C15">
+        <v>1221.72</v>
+      </c>
+      <c r="D15">
+        <v>2293.79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>500</v>
+      </c>
+      <c r="C16">
+        <v>655.54</v>
+      </c>
+      <c r="D16">
+        <v>1340.82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1"/>
+      <c r="B17">
+        <v>800</v>
+      </c>
+      <c r="C17">
+        <v>1197.05</v>
+      </c>
+      <c r="D17">
+        <v>2195.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1"/>
+      <c r="B18">
+        <v>1000</v>
+      </c>
+      <c r="C18">
+        <v>1234.6099999999999</v>
+      </c>
+      <c r="D18">
+        <v>2281.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="H1:N2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
